--- a/new_results/output_data.xlsx
+++ b/new_results/output_data.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,15 +449,945 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BACK</t>
+          <t>FRONT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2403052113</t>
+          <t>TDFW2393 052824</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TDFW2394 052824</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TDFW2393 052824</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>JUD4106 052824</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TDFW2394 052824</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TDFW2393 052824</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JUD4106 052824</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>JUD4107 052824</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JUD4105 052824</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TDFW2396  052824</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TDFW2397 052824</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>EIE0711 052824</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LUN2410 052924</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ECHO0367 052924</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TD-M-7537 052924</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>JUD2588 052924</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TDM7563 052924</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TD-M-23006 052924</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ECT0324 052924</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ECT0261 052924</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>JUD3151 052924</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TDM6599 052924</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>KAY0823 052924</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>KAY0921 052924</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>KAY0921 052924</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TDM6161 052924</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EHM2463 052924</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EHM2463 052924</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TD-FW-14103 052924</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TD-FW-4924-1 052924</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LUN2029X 052924</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>YCW4059 052824</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2405283376</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TDHX0787/C 052824</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>TDHX0787/B 052824</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TDHX0787/A 052824</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TD-FW-14133-1 052924</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TD-M-6928 052924</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>TD-M-16164 052924</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>YCW4059 052824</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2405283376</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TDHX0787/C 052824</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>TDHX0787/B 052824</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>TDHX0787/A 052824</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>TD-FW-14133-1 052924</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>TD-M-6928 052924</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>TD-M-16164 052924</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>YCW4055 052824</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>YCW4058 052824</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>YCW4057 052824</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>YCW4056 052824</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>YCW4059 052824</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2405283376</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>TDHX0787/C 052824</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>TDHX0787/B 052824</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ECT0261 052924</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>JUD3151 052924</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>TDM6599 052924</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>KAY0823 052924</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>KAY0921 052924</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>KAY0921 052924</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>TDM6161 052924</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>EHM2463 052924</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -472,7 +1402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,42 +1450,528 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2403052113</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
+          <t>YCW4055 052824</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>5128124</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>YCW4058 052824</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>128124</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>YCW4057 052824</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>128124</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>YCW4056 052824</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>128124</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>YCW4059 052824</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>128124</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2405283376</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>20124</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TDHX0787/C 052824</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>128124</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TDHX0787/B 052824</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>HAIR</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ECT0261 052924</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>5129/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>JUD3151 052924</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>29/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TDM6599 052924</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5129/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KAY0823 052924</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>29/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KAY0921 052924</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>29/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KAY0921 052924</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5/29/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TDM6161 052924</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>129/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EHM2463 052924</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>129/24</t>
         </is>
       </c>
     </row>

--- a/new_results/output_data.xlsx
+++ b/new_results/output_data.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1388,6 +1388,51 @@
         </is>
       </c>
       <c r="C64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>TD-M-7537 052924</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>JUD4105 052824</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>JUD4106 052824</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1402,7 +1447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1975,6 +2020,96 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TD-M-7537 052924</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>JUD4105 052824</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>5/28/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>JUD4106 052824</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_results/output_data.xlsx
+++ b/new_results/output_data.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1433,6 +1433,216 @@
         </is>
       </c>
       <c r="C67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ECT0261 052924</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>JUD3151 052924</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>TDM6599 052924</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>KAY0823 052924</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>KAY0921 052924</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>KAY0921 052924</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>TDM6161 052924</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>EHM2463 052924</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>TDFW2394 052824</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>TDFW2393 052824</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>TDFW2396  052824</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>EIE0711 052824</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BACK</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>LUN2029X 052924</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BACK</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2405293370</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1447,7 +1657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2110,6 +2320,418 @@
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ECT0261 052924</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>JUD3151 052924</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TDM6599 052924</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>KAY0823 052924</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>KAY0921 052924</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>KAY0921 052924</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TDM6161 052924</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EHM2463 052924</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TDFW2394 052824</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>HAIR</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TDFW2393 052824</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SUN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TDFW2396  052824</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EIE0711 052824</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>HOL</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LUN2029X 052924</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2405293370</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
